--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA580889-6FBA-DD4F-866C-28FA6AC17101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EDE9A0-B6BB-674B-B6C5-4430ABDE53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Draw" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>DrawPosition</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>dallas-2026</t>
+  </si>
+  <si>
+    <t>2026-02-09</t>
+  </si>
+  <si>
+    <t>2026-02-15</t>
   </si>
 </sst>
 </file>
@@ -200,7 +206,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -805,16 +811,16 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4">
-        <v>46062</v>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4">
-        <v>46068</v>
+      <c r="B7" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">

--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,15 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EDE9A0-B6BB-674B-B6C5-4430ABDE53FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD56CCE-F3BB-A34B-9A61-21BD61DDBC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Draw" sheetId="1" r:id="rId1"/>
     <sheet name="Info" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -541,7 +554,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="3">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -555,7 +568,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -569,7 +582,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>1825</v>
+        <v>1815</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -583,7 +596,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="3">
-        <v>1795</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -597,7 +610,7 @@
         <v>18</v>
       </c>
       <c r="D6" s="3">
-        <v>1660</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -611,7 +624,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="3">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -625,7 +638,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="3">
-        <v>1730</v>
+        <v>1705</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -639,7 +652,7 @@
         <v>21</v>
       </c>
       <c r="D9" s="3">
-        <v>1750</v>
+        <v>1765</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -653,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="3">
-        <v>1785</v>
+        <v>1790</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -667,7 +680,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="3">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -709,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="3">
-        <v>1850</v>
+        <v>1860</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -723,7 +736,7 @@
         <v>27</v>
       </c>
       <c r="D15" s="3">
-        <v>1685</v>
+        <v>1675</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -737,7 +750,7 @@
         <v>28</v>
       </c>
       <c r="D16" s="3">
-        <v>1640</v>
+        <v>1660</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -751,7 +764,7 @@
         <v>29</v>
       </c>
       <c r="D17" s="3">
-        <v>1930</v>
+        <v>1935</v>
       </c>
       <c r="E17">
         <v>1</v>

--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD56CCE-F3BB-A34B-9A61-21BD61DDBC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B391FE9-3F41-3741-8BAA-3E359F0AC4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,8 +556,8 @@
       <c r="D2" s="3">
         <v>1895</v>
       </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="E2" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -570,7 +570,7 @@
       <c r="D3" s="3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>1</v>
       </c>
     </row>
@@ -584,7 +584,7 @@
       <c r="D4" s="3">
         <v>1815</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>1</v>
       </c>
     </row>
@@ -598,8 +598,8 @@
       <c r="D5" s="3">
         <v>0</v>
       </c>
-      <c r="E5">
-        <v>1</v>
+      <c r="E5" s="3">
+        <v>1.5</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -610,9 +610,9 @@
         <v>18</v>
       </c>
       <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6">
+        <v>1650</v>
+      </c>
+      <c r="E6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -626,7 +626,7 @@
       <c r="D7" s="3">
         <v>1755</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -640,7 +640,7 @@
       <c r="D8" s="3">
         <v>1705</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -654,7 +654,7 @@
       <c r="D9" s="3">
         <v>1765</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="D10" s="3">
         <v>1790</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -682,7 +682,7 @@
       <c r="D11" s="3">
         <v>1645</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>1</v>
       </c>
     </row>
@@ -696,7 +696,7 @@
       <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>1</v>
       </c>
     </row>
@@ -710,7 +710,7 @@
       <c r="D13" s="3">
         <v>1815</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <v>1</v>
       </c>
     </row>
@@ -724,7 +724,7 @@
       <c r="D14" s="3">
         <v>1860</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <v>1</v>
       </c>
     </row>
@@ -738,7 +738,7 @@
       <c r="D15" s="3">
         <v>1675</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="3">
         <v>1</v>
       </c>
     </row>
@@ -752,7 +752,7 @@
       <c r="D16" s="3">
         <v>1660</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="3">
         <v>1</v>
       </c>
     </row>
@@ -766,7 +766,7 @@
       <c r="D17" s="3">
         <v>1935</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="3">
         <v>1</v>
       </c>
     </row>

--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B391FE9-3F41-3741-8BAA-3E359F0AC4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66652501-47C2-A244-84FD-94AA73E1027F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,10 +554,10 @@
         <v>14</v>
       </c>
       <c r="D2" s="3">
-        <v>1895</v>
+        <v>1905</v>
       </c>
       <c r="E2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">

--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66652501-47C2-A244-84FD-94AA73E1027F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BFC296-F758-4247-A4A7-2436F79E4DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -666,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="D10" s="3">
-        <v>1790</v>
+        <v>1795</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
@@ -680,7 +680,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="3">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
@@ -722,7 +722,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="3">
-        <v>1860</v>
+        <v>1865</v>
       </c>
       <c r="E14" s="3">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>29</v>
       </c>
       <c r="D17" s="3">
-        <v>1935</v>
+        <v>1940</v>
       </c>
       <c r="E17" s="3">
         <v>1</v>

--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BFC296-F758-4247-A4A7-2436F79E4DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C46CE76-9180-0B4B-8454-60B1F5C0E72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -90,9 +90,6 @@
     <t>Frances Tiafoe</t>
   </si>
   <si>
-    <t>Qualifier1</t>
-  </si>
-  <si>
     <t>Eliot Spizzirri</t>
   </si>
   <si>
@@ -145,6 +142,9 @@
   </si>
   <si>
     <t>2026-02-15</t>
+  </si>
+  <si>
+    <t>Jack Pinnington Jones</t>
   </si>
 </sst>
 </file>
@@ -582,7 +582,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
@@ -606,11 +606,11 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D6" s="3">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="E6" s="3">
         <v>1</v>
@@ -621,10 +621,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>1755</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3">
         <v>1</v>
@@ -635,10 +635,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3">
-        <v>1705</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
@@ -649,7 +649,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="3">
         <v>1765</v>
@@ -663,10 +663,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
@@ -677,10 +677,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3">
-        <v>1640</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="3">
         <v>1815</v>
@@ -719,7 +719,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="3">
         <v>1865</v>
@@ -733,7 +733,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="3">
         <v>1675</v>
@@ -747,7 +747,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="3">
         <v>1660</v>
@@ -761,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="3">
         <v>1940</v>
@@ -785,7 +785,7 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -793,7 +793,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -809,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -817,7 +817,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -825,7 +825,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -833,7 +833,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -841,7 +841,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C46CE76-9180-0B4B-8454-60B1F5C0E72C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DA4470-B7B9-D54C-9A0F-8185F79B26DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>DrawPosition</t>
   </si>
@@ -81,43 +81,19 @@
     <t>Taylor Fritz</t>
   </si>
   <si>
-    <t>Brandon Nakashima</t>
-  </si>
-  <si>
     <t>Sebastian Korda</t>
   </si>
   <si>
-    <t>Frances Tiafoe</t>
-  </si>
-  <si>
-    <t>Eliot Spizzirri</t>
-  </si>
-  <si>
-    <t>Ethan Quinn</t>
-  </si>
-  <si>
     <t>Marin Cilic</t>
   </si>
   <si>
     <t>Denis Shapovalov</t>
   </si>
   <si>
-    <t>Aleksandar Kovacevic</t>
-  </si>
-  <si>
-    <t>Alex Michelsen</t>
-  </si>
-  <si>
     <t>Alejandro Davidovich Fokina</t>
   </si>
   <si>
-    <t>Tommy Paul</t>
-  </si>
-  <si>
     <t>Miomir Kecmanovic</t>
-  </si>
-  <si>
-    <t>Adrian Mannarino</t>
   </si>
   <si>
     <t>Ben Shelton</t>
@@ -522,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -554,7 +530,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="3">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
@@ -568,7 +544,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="3">
-        <v>0</v>
+        <v>1825</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -578,11 +554,11 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="D4" s="3">
-        <v>1820</v>
+        <v>1610</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
@@ -593,10 +569,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <v>1780</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
@@ -606,11 +582,11 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>36</v>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="3">
-        <v>1660</v>
+        <v>1820</v>
       </c>
       <c r="E6" s="3">
         <v>1</v>
@@ -624,7 +600,7 @@
         <v>18</v>
       </c>
       <c r="D7" s="3">
-        <v>0</v>
+        <v>1805</v>
       </c>
       <c r="E7" s="3">
         <v>1</v>
@@ -638,7 +614,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="3">
-        <v>0</v>
+        <v>1675</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
@@ -652,121 +628,9 @@
         <v>20</v>
       </c>
       <c r="D9" s="3">
-        <v>1765</v>
+        <v>1935</v>
       </c>
       <c r="E9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1815</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1865</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="3">
-        <v>1675</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1660</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1940</v>
-      </c>
-      <c r="E17" s="3">
         <v>1</v>
       </c>
     </row>
@@ -785,7 +649,7 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -793,7 +657,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -809,7 +673,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -817,7 +681,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -825,7 +689,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -833,7 +697,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -841,7 +705,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/draws/dallas2026.xlsx
+++ b/draws/dallas2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cadecarlson/EDACCloud/tf-site/draws/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DA4470-B7B9-D54C-9A0F-8185F79B26DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E04C67-B037-804E-B3F7-53895C21B710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>DrawPosition</t>
   </si>
@@ -81,21 +81,12 @@
     <t>Taylor Fritz</t>
   </si>
   <si>
-    <t>Sebastian Korda</t>
-  </si>
-  <si>
     <t>Marin Cilic</t>
   </si>
   <si>
     <t>Denis Shapovalov</t>
   </si>
   <si>
-    <t>Alejandro Davidovich Fokina</t>
-  </si>
-  <si>
-    <t>Miomir Kecmanovic</t>
-  </si>
-  <si>
     <t>Ben Shelton</t>
   </si>
   <si>
@@ -118,9 +109,6 @@
   </si>
   <si>
     <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>Jack Pinnington Jones</t>
   </si>
 </sst>
 </file>
@@ -498,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
@@ -530,7 +518,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="3">
-        <v>1900</v>
+        <v>1880</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
@@ -544,7 +532,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="3">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -554,11 +542,11 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>28</v>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D4" s="3">
-        <v>1610</v>
+        <v>1825</v>
       </c>
       <c r="E4" s="3">
         <v>1</v>
@@ -569,68 +557,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3">
-        <v>1780</v>
+        <v>1915</v>
       </c>
       <c r="E5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1820</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1805</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1675</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1935</v>
-      </c>
-      <c r="E9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -649,7 +581,7 @@
         <v>5</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -657,7 +589,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -673,7 +605,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -681,7 +613,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -689,7 +621,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -697,7 +629,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -705,7 +637,7 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
